--- a/astro-site/public/dl/coffee-cart-business-plan/coffee-cart-pricing-calculator.xlsx
+++ b/astro-site/public/dl/coffee-cart-business-plan/coffee-cart-pricing-calculator.xlsx
@@ -2431,7 +2431,7 @@
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>The all-in cost is the drink served in a single-use cup; with reusable cups only the ingredient cost counts. Milk is a TCS food: keep it at 41 °F (5 °C) or below (the FDA Food Code minimum). The cost of goods in the financial plan is something else: the average of the mix with waste.</t>
+          <t>The all-in cost is the drink served in a single-use cup; with reusable cups only the ingredient cost counts. Milk is a TCS food: keep it at 41 °F (5 °C) or below (the FDA Food Code cold-holding limit). The cost of goods in the financial plan is something else: the average of the mix with waste.</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Example rate applied to the whole invoice. Many states tax catering, including the staff and the travel fee; at festivals you collect it on each drink. Look up your state and city.</t>
+          <t>Example rate applied to the whole invoice. Many states tax catering, including the staff and extras (some tax the travel fee too); at festivals you collect it on each drink. Look up your state and city.</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>SCALING RULES (the same table as the business plan's operations section)</t>
+          <t>SCALING RULES (kit estimates from US ratios)</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4817,7 +4817,7 @@
     <row r="165" ht="48" customHeight="1">
       <c r="A165" s="16" t="inlineStr">
         <is>
-          <t>The same table appears in the operations section of the business plan. One barista on a 2-group machine makes 50-65 drinks an hour (flashquotes.com); a second station comes in when the peak does not fit. A standard 110V outlet gives about 2.4 kW: a 220V 2-group machine needs a dedicated circuit or a generator. Kit estimate from US ratios.</t>
+          <t>One barista on a 2-group machine makes 50-65 drinks an hour (flashquotes.com); a second station comes in when the peak does not fit. A standard 110V outlet gives about 2.4 kW: a 220V 2-group machine needs a dedicated circuit or a generator. Kit estimate from US ratios.</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Farmers market, guest-pay</t>
+          <t>Community festival, guest-pay</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Farmers market, guest-pay</t>
+          <t>Community festival, guest-pay</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
     <row r="96" ht="75" customHeight="1">
       <c r="A96" s="25" t="inlineStr">
         <is>
-          <t>Farmers market, guest-pay</t>
+          <t>Community festival, guest-pay</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Festival or market: 150 drinks over 4 hours in the morning, compostable cups, a generator and a 15% organizer fee, with an $800 minimum sales guarantee. The "price per guest" is the lowest price per drink; at $6.50 a drink the day leaves about $384 before fixed costs, and below 60 drinks you lose money (the guarantee would then cover part of it).</t>
+          <t>Festival or market (a community festival): 150 drinks over 4 hours in the morning, compostable cups, a generator and a 15% organizer fee, with an $800 minimum sales guarantee. The "price per guest" is the lowest price per drink; at $6.50 a drink the day leaves about $384 before fixed costs, and, without the guarantee, below 60 drinks you would lose money: the $800 guarantee covers that risk.</t>
         </is>
       </c>
     </row>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>5. The scaling table at the bottom gives baristas, 2-group machines, grinders, pounds of coffee, gallons of milk, cups, power, the circuit you need and water. It is the same table as the operations section of the business plan.</t>
+          <t>5. The scaling table at the bottom gives baristas, 2-group machines, grinders, pounds of coffee, gallons of milk, cups, power, the circuit you need and water. Its rules use the same assumptions as the business plan: drinks per guest by service length, 50-65 drinks per barista an hour and 18 g per double shot.</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Milk is a TCS food: keep it at 41 °F (5 °C) or below in the cart's fridge and in coolers (the FDA Food Code minimum). Use a separate pitcher for each milk, wash your hands at the cart's hand sink first, and buy pastries only from a licensed bakery.</t>
+          <t>Milk is a TCS food: keep it at 41 °F (5 °C) or below in the cart's fridge and in coolers (the FDA Food Code cold-holding limit). Use a separate pitcher for each milk, wash your hands at the cart's hand sink first, and buy pastries only from a licensed bakery.</t>
         </is>
       </c>
     </row>
